--- a/ksoft_old/docs/fields_details/jalmeida/RE0508-14082024-152324.xlsx
+++ b/ksoft_old/docs/fields_details/jalmeida/RE0508-14082024-152324.xlsx
@@ -2043,13 +2043,13 @@
 </file>
 
 <file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{D29AC6FC-DEA3-4CCD-B243-673B47F7BA61}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{6E675035-9AF5-48C1-B521-AD188416C7B3}"/>
 </file>
 
 <file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{95E07C36-3850-44CE-9493-058B8AA738D0}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{F68E5C12-5B6B-407D-BD3D-4FAA6510B7AE}"/>
 </file>
 
 <file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{0562A9D4-4B13-4703-A5B0-44B5266F9889}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{BED64C4B-3260-49A8-A420-C5509E9216B3}"/>
 </file>
--- a/ksoft_old/docs/fields_details/jalmeida/RE0508-14082024-152324.xlsx
+++ b/ksoft_old/docs/fields_details/jalmeida/RE0508-14082024-152324.xlsx
@@ -2043,13 +2043,13 @@
 </file>
 
 <file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{6E675035-9AF5-48C1-B521-AD188416C7B3}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{856F8625-383F-4F96-A14E-6D8021859748}"/>
 </file>
 
 <file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{F68E5C12-5B6B-407D-BD3D-4FAA6510B7AE}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{0D138A08-03F2-48E1-8F10-9E857B71E62E}"/>
 </file>
 
 <file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{BED64C4B-3260-49A8-A420-C5509E9216B3}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{709F0ACB-864C-4D6C-911A-91CDD7163E3F}"/>
 </file>
--- a/ksoft_old/docs/fields_details/jalmeida/RE0508-14082024-152324.xlsx
+++ b/ksoft_old/docs/fields_details/jalmeida/RE0508-14082024-152324.xlsx
@@ -2043,13 +2043,13 @@
 </file>
 
 <file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{856F8625-383F-4F96-A14E-6D8021859748}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{D29AC6FC-DEA3-4CCD-B243-673B47F7BA61}"/>
 </file>
 
 <file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{0D138A08-03F2-48E1-8F10-9E857B71E62E}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{95E07C36-3850-44CE-9493-058B8AA738D0}"/>
 </file>
 
 <file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{709F0ACB-864C-4D6C-911A-91CDD7163E3F}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{0562A9D4-4B13-4703-A5B0-44B5266F9889}"/>
 </file>